--- a/transitions/integration_DOS.xlsx
+++ b/transitions/integration_DOS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30005"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30009"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\transition-tracker\transitions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{D39B6D11-2832-43D2-98CD-31A47870B59F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D72E21BB-23A6-4FC8-B19A-74A345ADD9E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{599EBF2C-F03D-4D09-9E28-84955A54914B}"/>
   </bookViews>
@@ -1468,7 +1468,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:74" s="1" customFormat="1" ht="116.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:74" s="1" customFormat="1" ht="68.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
